--- a/Ratings.xlsx
+++ b/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daschultheiss/hero-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCA7980-169B-154E-9489-D6596E5F7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A108AA7-C39F-EE40-8DFF-7906C38755AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -758,7 +758,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -781,6 +781,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -848,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -894,27 +900,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -939,13 +932,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="newHeroes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2422,7 +2431,7 @@
       <c r="C48" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="17" t="s">
         <v>172</v>
       </c>
       <c r="E48" s="13" t="s">
